--- a/TestCases/Drug_Category_TestCase.xlsx
+++ b/TestCases/Drug_Category_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82277D2-2F22-47B9-939B-65B8C25DBE68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D067B0-6EF1-4BB6-A639-9B13B63C2851}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12792" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DRUG_CATEGORY" sheetId="15" r:id="rId1"/>
+    <sheet name="DRUG_CATEGORY" sheetId="16" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -34,19 +34,19 @@
     <t>SpringMediCareWeb</t>
   </si>
   <si>
-    <t>Module Code：</t>
+    <t>Pass</t>
   </si>
   <si>
-    <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Module Code：</t>
+  </si>
+  <si>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -79,10 +79,10 @@
     <t>Hệ thống thực hiện tìm kiếm đúng.</t>
   </si>
   <si>
-    <t>DRUG400 - Drug Inventory Management</t>
+    <t>DRUG - Drug Inventory Management</t>
   </si>
   <si>
-    <t>DRUG1 - Manage Drug Inventory</t>
+    <t>Drug Inventory Management</t>
   </si>
   <si>
     <t>1. Kiểm tra hiển thị danh mục thuốc</t>
@@ -411,6 +411,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,11 +425,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <sz val="11"/>
@@ -623,30 +623,30 @@
   </cellStyleXfs>
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -667,33 +667,33 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -912,7 +912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -933,9 +933,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -959,9 +959,9 @@
     </row>
     <row r="2" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -987,11 +987,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1015,13 +1015,13 @@
     </row>
     <row r="4" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="5" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="23"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="6" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="7" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
@@ -1168,21 +1168,21 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="30" t="s">
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="28" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="33" t="s">
@@ -1210,16 +1210,16 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1238,14 +1238,14 @@
     <row r="11" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="37"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="23"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="26"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1265,15 +1265,15 @@
       <c r="A12" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="23"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1302,8 +1302,8 @@
       <c r="D13" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="17" t="s">
         <v>25</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>46255</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>26</v>
@@ -1335,15 +1335,15 @@
       <c r="A14" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="23"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="26"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1372,8 +1372,8 @@
       <c r="D15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="17" t="s">
         <v>32</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>46255</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>33</v>
@@ -1405,15 +1405,15 @@
       <c r="A16" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="23"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="26"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1442,8 +1442,8 @@
       <c r="D17" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="17" t="s">
         <v>39</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>46255</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>40</v>
@@ -1475,15 +1475,15 @@
       <c r="A18" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="23"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="26"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -1512,8 +1512,8 @@
       <c r="D19" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
       <c r="G19" s="17" t="s">
         <v>46</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>46255</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>17</v>
@@ -1554,8 +1554,8 @@
       <c r="D20" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
       <c r="G20" s="17" t="s">
         <v>51</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>46255</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>17</v>
@@ -1596,8 +1596,8 @@
       <c r="D21" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="17" t="s">
         <v>56</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>46255</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>17</v>
@@ -1629,15 +1629,15 @@
       <c r="A22" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="23"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="26"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1666,8 +1666,8 @@
       <c r="D23" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
       <c r="G23" s="17" t="s">
         <v>62</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>46255</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>63</v>
@@ -1708,8 +1708,8 @@
       <c r="D24" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
       <c r="G24" s="20" t="s">
         <v>68</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>46255</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>69</v>
@@ -1750,8 +1750,8 @@
       <c r="D25" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
       <c r="G25" s="17" t="s">
         <v>74</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>46255</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>75</v>
@@ -1792,8 +1792,8 @@
       <c r="D26" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
       <c r="G26" s="17" t="s">
         <v>80</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>46255</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>81</v>
@@ -1825,28 +1825,28 @@
       <c r="A27" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="26"/>
       <c r="K27" s="36"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
       <c r="X27" s="3"/>
     </row>
     <row r="28" spans="1:24" ht="165" customHeight="1" x14ac:dyDescent="0.25">
@@ -1862,8 +1862,8 @@
       <c r="D28" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="17" t="s">
         <v>87</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>46255</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J28" s="16" t="s">
         <v>88</v>
@@ -26964,17 +26964,17 @@
     <mergeCell ref="D9:F10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
-    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0E00-000001000000}"/>
-    <hyperlink ref="G17" r:id="rId3" xr:uid="{00000000-0004-0000-0E00-000002000000}"/>
-    <hyperlink ref="G19" r:id="rId4" xr:uid="{00000000-0004-0000-0E00-000003000000}"/>
-    <hyperlink ref="G20" r:id="rId5" xr:uid="{00000000-0004-0000-0E00-000004000000}"/>
-    <hyperlink ref="G21" r:id="rId6" xr:uid="{00000000-0004-0000-0E00-000005000000}"/>
-    <hyperlink ref="G23" r:id="rId7" xr:uid="{00000000-0004-0000-0E00-000006000000}"/>
-    <hyperlink ref="G24" r:id="rId8" xr:uid="{00000000-0004-0000-0E00-000007000000}"/>
-    <hyperlink ref="G25" r:id="rId9" xr:uid="{00000000-0004-0000-0E00-000008000000}"/>
-    <hyperlink ref="G26" r:id="rId10" xr:uid="{00000000-0004-0000-0E00-000009000000}"/>
-    <hyperlink ref="G28" r:id="rId11" xr:uid="{00000000-0004-0000-0E00-00000A000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
+    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
+    <hyperlink ref="G17" r:id="rId3" xr:uid="{00000000-0004-0000-0F00-000002000000}"/>
+    <hyperlink ref="G19" r:id="rId4" xr:uid="{00000000-0004-0000-0F00-000003000000}"/>
+    <hyperlink ref="G20" r:id="rId5" xr:uid="{00000000-0004-0000-0F00-000004000000}"/>
+    <hyperlink ref="G21" r:id="rId6" xr:uid="{00000000-0004-0000-0F00-000005000000}"/>
+    <hyperlink ref="G23" r:id="rId7" xr:uid="{00000000-0004-0000-0F00-000006000000}"/>
+    <hyperlink ref="G24" r:id="rId8" xr:uid="{00000000-0004-0000-0F00-000007000000}"/>
+    <hyperlink ref="G25" r:id="rId9" xr:uid="{00000000-0004-0000-0F00-000008000000}"/>
+    <hyperlink ref="G26" r:id="rId10" xr:uid="{00000000-0004-0000-0F00-000009000000}"/>
+    <hyperlink ref="G28" r:id="rId11" xr:uid="{00000000-0004-0000-0F00-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
